--- a/Documentation/Best For Lists/Best for Seniors Living Alone List.xlsx
+++ b/Documentation/Best For Lists/Best for Seniors Living Alone List.xlsx
@@ -621,7 +621,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-06-27  |  Products shown: 15  |  Eliminated by dedup rule: 14</t>
+          <t>Generated: 2026-06-28  |  Products shown: 15  |  Eliminated by dedup rule: 14</t>
         </is>
       </c>
     </row>

--- a/Documentation/Best For Lists/Best for Seniors Living Alone List.xlsx
+++ b/Documentation/Best For Lists/Best for Seniors Living Alone List.xlsx
@@ -621,7 +621,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-06-28  |  Products shown: 15  |  Eliminated by dedup rule: 14</t>
+          <t>Generated: 2026-07-02  |  Products shown: 15  |  Eliminated by dedup rule: 14</t>
         </is>
       </c>
     </row>
@@ -696,8 +696,7 @@
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
-          <t>Animal
-Type</t>
+          <t>Category</t>
         </is>
       </c>
       <c r="F4" s="5" t="inlineStr">
@@ -778,12 +777,12 @@
       </c>
       <c r="C5" s="7" t="inlineStr">
         <is>
-          <t>Percy Robot Cat</t>
+          <t>MateCat Pro</t>
         </is>
       </c>
       <c r="D5" s="8" t="inlineStr">
         <is>
-          <t>Budget Friendly</t>
+          <t>Best Value</t>
         </is>
       </c>
       <c r="E5" s="8" t="inlineStr">
@@ -792,13 +791,13 @@
         </is>
       </c>
       <c r="F5" s="8" t="n">
-        <v>89</v>
+        <v>178</v>
       </c>
       <c r="G5" s="8" t="n">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="H5" s="8" t="n">
-        <v>16</v>
+        <v>456</v>
       </c>
       <c r="I5" s="9" t="n">
         <v>4.45</v>
@@ -829,7 +828,7 @@
       </c>
       <c r="R5" s="7" t="inlineStr">
         <is>
-          <t>Cat-form Percy model. Assumed feature parity with Percy 1.1 Robotic Dog. Review strength=3: lower cumulative reviews than Percy 1.1. Verify current features against chongker.com Percy Robot Cat listing before publishing. Review Strength=2: 16 reviews, 5★ (repo data, 2026-06-22).</t>
+          <t>Touch/voice verified via chongker.com product page and instruction manual (manuals.plus). Multi-zone sensors trigger purring/meowing/heartbeat/movement. Voice wake: responds to specific phrases. 180-day warranty per chongker.com. Sound Level Control=5: ON/MUTE/OFF + volume control. Privacy=5 confirmed: no camera, microphone, or WiFi per Product Matrix. Review Strength=3: 456 reviews, 4.6★ (repo data, 2026-06-22). DEMENTIA SUITABILITY EVIDENCE TIER (2026-07-02): Tier C — dementia-suitability claims found only on Chongker's own marketing pages (unverified consultant/specialist quotes, no named institution); no independent research located. Capped at 4 per Tim's directive. Note: product complexity (voice commands, sleep-mode cycling, battery-status alerts on some models) also weighs against the Simplicity sub-criterion. Score is provisional pending dementia consultant review. DEMENTIA SUITABILITY RECALCULATED (2026-07-02, Tim-directed methodology): Simplicity=4, Familiar Form=5, Safety=5, Calmness=avg(Sound=4, Behavioral Realism=4)=4.0. Raw average of 4 sub-criteria=4.5, rounded=5, Evidence Tier C cap=4 -&gt; Final=4 (no change). This is a first-pass 'best effort' score pending dementia care consultant review (consultant search in progress as of 2026-07-02). Products in the 'Ai &amp; Robotic Pets' Type category are excluded from memory-care-relevant Best For lists via a separate Type filter in the Best For Weighting Table, independent of this score.</t>
         </is>
       </c>
     </row>
@@ -844,7 +843,7 @@
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>Percy 1.1 Robotic Companion Dog</t>
+          <t>Percy Robot Cat</t>
         </is>
       </c>
       <c r="D6" s="12" t="inlineStr">
@@ -854,7 +853,7 @@
       </c>
       <c r="E6" s="12" t="inlineStr">
         <is>
-          <t>Dog</t>
+          <t>Cat</t>
         </is>
       </c>
       <c r="F6" s="12" t="n">
@@ -864,10 +863,10 @@
         <v>5</v>
       </c>
       <c r="H6" s="12" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="I6" s="13" t="n">
-        <v>4.45</v>
+        <v>4.3</v>
       </c>
       <c r="J6" s="12" t="n">
         <v>3</v>
@@ -888,14 +887,14 @@
         <v>4</v>
       </c>
       <c r="P6" s="12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q6" s="12" t="n">
         <v>4</v>
       </c>
       <c r="R6" s="11" t="inlineStr">
         <is>
-          <t>Dog-form companion with touch sensors and heartbeat simulation. Weighted design for sensory relief per product documentation and buying-guide review (keyirobot.com). Feature set verified as broadly equivalent to MateCat Pro platform. Privacy=5: no camera or internet per Product Matrix. Product name updated to match repo: 'Percy 1.1 Robotic Companion Dog'. Review Strength=1: only 5 reviews at time of scoring (repo data, 2026-06-22).</t>
+          <t>Cat-form Percy model. Assumed feature parity with Percy 1.1 Robotic Dog. Review strength=3: lower cumulative reviews than Percy 1.1. Verify current features against chongker.com Percy Robot Cat listing before publishing. Review Strength=2: 16 reviews, 5★ (repo data, 2026-06-22). TACTILE COMFORT UPDATE (2026-07-01, Tim-directed): Rescored from 5 to 4. Percy line tier placed below MateCat (5) and above Joy for All (3) per Tim's tiering decision for the Chongker product family. DEMENTIA SUITABILITY EVIDENCE TIER (2026-07-02): Tier C — dementia-suitability claims found only on Chongker's own marketing pages (unverified consultant/specialist quotes, no named institution); no independent research located. Capped at 4 per Tim's directive. Note: product complexity (voice commands, sleep-mode cycling, battery-status alerts on some models) also weighs against the Simplicity sub-criterion. Score is provisional pending dementia consultant review. DEMENTIA SUITABILITY RECALCULATED (2026-07-02, Tim-directed methodology): Simplicity=4, Familiar Form=5, Safety=5, Calmness=avg(Sound=4, Behavioral Realism=4)=4.0. Raw average of 4 sub-criteria=4.5, rounded=5, Evidence Tier C cap=4 -&gt; Final=4 (no change). This is a first-pass 'best effort' score pending dementia care consultant review (consultant search in progress as of 2026-07-02). Products in the 'Ai &amp; Robotic Pets' Type category are excluded from memory-care-relevant Best For lists via a separate Type filter in the Best For Weighting Table, independent of this score.</t>
         </is>
       </c>
     </row>
@@ -910,30 +909,30 @@
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t>MateCat Pro</t>
+          <t>Percy 1.1 Robotic Companion Dog</t>
         </is>
       </c>
       <c r="D7" s="8" t="inlineStr">
         <is>
-          <t>Best Value</t>
+          <t>Budget Friendly</t>
         </is>
       </c>
       <c r="E7" s="8" t="inlineStr">
         <is>
-          <t>Cat</t>
+          <t>Dog</t>
         </is>
       </c>
       <c r="F7" s="8" t="n">
-        <v>178</v>
+        <v>89</v>
       </c>
       <c r="G7" s="8" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="H7" s="8" t="n">
-        <v>456</v>
+        <v>5</v>
       </c>
       <c r="I7" s="9" t="n">
-        <v>4.45</v>
+        <v>4.3</v>
       </c>
       <c r="J7" s="8" t="n">
         <v>3</v>
@@ -954,14 +953,14 @@
         <v>4</v>
       </c>
       <c r="P7" s="8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q7" s="8" t="n">
         <v>4</v>
       </c>
       <c r="R7" s="7" t="inlineStr">
         <is>
-          <t>Touch/voice verified via chongker.com product page and instruction manual (manuals.plus). Multi-zone sensors trigger purring/meowing/heartbeat/movement. Voice wake: responds to specific phrases. 180-day warranty per chongker.com. Sound Level Control=5: ON/MUTE/OFF + volume control. Privacy=5 confirmed: no camera, microphone, or WiFi per Product Matrix. Review Strength=3: 456 reviews, 4.6★ (repo data, 2026-06-22).</t>
+          <t>Dog-form companion with touch sensors and heartbeat simulation. Weighted design for sensory relief per product documentation and buying-guide review (keyirobot.com). Feature set verified as broadly equivalent to MateCat Pro platform. Privacy=5: no camera or internet per Product Matrix. Product name updated to match repo: 'Percy 1.1 Robotic Companion Dog'. Review Strength=1: only 5 reviews at time of scoring (repo data, 2026-06-22). TACTILE COMFORT UPDATE (2026-07-01, Tim-directed): Rescored from 5 to 4. Percy line tier placed below MateCat (5) and above Joy for All (3) per Tim's tiering decision for the Chongker product family. DEMENTIA SUITABILITY EVIDENCE TIER (2026-07-02): Tier C — dementia-suitability claims found only on Chongker's own marketing pages (unverified consultant/specialist quotes, no named institution); no independent research located. Capped at 4 per Tim's directive. Note: product complexity (voice commands, sleep-mode cycling, battery-status alerts on some models) also weighs against the Simplicity sub-criterion. Score is provisional pending dementia consultant review. DEMENTIA SUITABILITY RECALCULATED (2026-07-02, Tim-directed methodology): Simplicity=4, Familiar Form=5, Safety=5, Calmness=avg(Sound=4, Behavioral Realism=4)=4.0. Raw average of 4 sub-criteria=4.5, rounded=5, Evidence Tier C cap=4 -&gt; Final=4 (no change). This is a first-pass 'best effort' score pending dementia care consultant review (consultant search in progress as of 2026-07-02). Products in the 'Ai &amp; Robotic Pets' Type category are excluded from memory-care-relevant Best For lists via a separate Type filter in the Best For Weighting Table, independent of this score.</t>
         </is>
       </c>
     </row>
@@ -999,7 +998,7 @@
         <v>11640</v>
       </c>
       <c r="I8" s="13" t="n">
-        <v>4.4</v>
+        <v>4.25</v>
       </c>
       <c r="J8" s="12" t="n">
         <v>2</v>
@@ -1020,14 +1019,14 @@
         <v>5</v>
       </c>
       <c r="P8" s="12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q8" s="12" t="n">
         <v>5</v>
       </c>
       <c r="R8" s="11" t="inlineStr">
         <is>
-          <t>All Joy for All variants share identical sensor/audio platform. Sound Quality=1 per locked rubric anchor (documented 'loud unrealistic meow', Best Buy reviews). Sound Level Control=5 per rubric anchor (3-position ON/OFF/MUTE switch). Review Strength=5 per verified 4.4/5 stars, 10,000+ Amazon reviews. Visual contrast varies by coat color — scored per variant. Orange tabby coat — higher visual contrast against most furniture. Review Strength=5: 11,640 reviews, 4.5★ (repo data, 2026-06-22).</t>
+          <t>All Joy for All variants share identical sensor/audio platform. Sound Quality=1 per locked rubric anchor (documented 'loud unrealistic meow', Best Buy reviews). Sound Level Control=5 per rubric anchor (3-position ON/OFF/MUTE switch). Review Strength=5 per verified 4.4/5 stars, 10,000+ Amazon reviews. Visual contrast varies by coat color — scored per variant. Orange tabby coat — higher visual contrast against most furniture. Review Strength=5: 11,640 reviews, 4.5★ (repo data, 2026-06-22). TACTILE COMFORT UPDATE (2026-07-01, Tim-directed): Rescored from 4 to 3. DEMENTIA SUITABILITY EVIDENCE TIER (2026-07-02): Tier A — independent peer-reviewed research (Journal of Holistic Nursing, 2022). No cap; score reflects full 1-5 range. DEMENTIA SUITABILITY RECALCULATED (2026-07-02, Tim-directed methodology): Simplicity=5, Familiar Form=5, Safety=5, Calmness=avg(Sound=3, Behavioral Realism=3)=3.0. Raw average of 4 sub-criteria=4.5, rounded=5, Evidence Tier A cap=5 -&gt; Final=5 (no change). This is a first-pass 'best effort' score pending dementia care consultant review (consultant search in progress as of 2026-07-02). Products in the 'Ai &amp; Robotic Pets' Type category are excluded from memory-care-relevant Best For lists via a separate Type filter in the Best For Weighting Table, independent of this score.</t>
         </is>
       </c>
     </row>
@@ -1065,7 +1064,7 @@
         <v>5164</v>
       </c>
       <c r="I9" s="9" t="n">
-        <v>4.4</v>
+        <v>4.25</v>
       </c>
       <c r="J9" s="8" t="n">
         <v>2</v>
@@ -1086,14 +1085,14 @@
         <v>5</v>
       </c>
       <c r="P9" s="8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q9" s="8" t="n">
         <v>5</v>
       </c>
       <c r="R9" s="7" t="inlineStr">
         <is>
-          <t>All Joy for All variants share identical sensor/audio platform. Sound Quality=1 per locked rubric anchor (documented 'loud unrealistic meow', Best Buy reviews). Sound Level Control=5 per rubric anchor (3-position ON/OFF/MUTE switch). Review Strength=5 per verified 4.4/5 stars, 10,000+ Amazon reviews. Visual contrast varies by coat color — scored per variant. Review Strength=5: 5,164 reviews, 4.3★ (repo data, 2026-06-22).</t>
+          <t>All Joy for All variants share identical sensor/audio platform. Sound Quality=1 per locked rubric anchor (documented 'loud unrealistic meow', Best Buy reviews). Sound Level Control=5 per rubric anchor (3-position ON/OFF/MUTE switch). Review Strength=5 per verified 4.4/5 stars, 10,000+ Amazon reviews. Visual contrast varies by coat color — scored per variant. Review Strength=5: 5,164 reviews, 4.3★ (repo data, 2026-06-22). TACTILE COMFORT UPDATE (2026-07-01, Tim-directed): Rescored from 4 to 3. DEMENTIA SUITABILITY EVIDENCE TIER (2026-07-02): Tier A — independent peer-reviewed research (Journal of Holistic Nursing, 2022). No cap; score reflects full 1-5 range. DEMENTIA SUITABILITY RECALCULATED (2026-07-02, Tim-directed methodology): Simplicity=5, Familiar Form=5, Safety=5, Calmness=avg(Sound=3, Behavioral Realism=3)=3.0. Raw average of 4 sub-criteria=4.5, rounded=5, Evidence Tier A cap=5 -&gt; Final=5 (no change). This is a first-pass 'best effort' score pending dementia care consultant review (consultant search in progress as of 2026-07-02). Products in the 'Ai &amp; Robotic Pets' Type category are excluded from memory-care-relevant Best For lists via a separate Type filter in the Best For Weighting Table, independent of this score.</t>
         </is>
       </c>
     </row>
@@ -1159,7 +1158,7 @@
       </c>
       <c r="R10" s="11" t="inlineStr">
         <is>
-          <t>Detailed scoring performed in prior session against original product spec sheet. Review Strength: no verified current Amazon rating found — manual lookup required before publishing. Control accessibility=3: single ear-switch concealed in fur. Noise Sensitivity=5: explicit mute mode, designed to avoid motor noise per manufacturer. Amazon listing confirmed by Tim: https://www.amazon.com/Chongker-Breathing-Soothing-Interactive-Companion/dp/B0F83R6F75 — Amazon automated access blocked; star rating and review count require manual lookup before updating Review Strength score. Review Strength=1: only 2 reviews at time of scoring (repo data, 2026-06-22). Amazon URL confirmed: amazon.com/dp/B0F83R6F75 — automated fetch blocked; verify rating/count manually before next refresh Value for Money forced to 4 by Tim (June 2026) — consistent with other Chongker product family scores. See Product_Feature_Score_Details.xlsx for rationale.</t>
+          <t>Detailed scoring performed in prior session against original product spec sheet. Review Strength: no verified current Amazon rating found — manual lookup required before publishing. Control accessibility=3: single ear-switch concealed in fur. Noise Sensitivity=5: explicit mute mode, designed to avoid motor noise per manufacturer. Amazon listing confirmed by Tim: https://www.amazon.com/Chongker-Breathing-Soothing-Interactive-Companion/dp/B0F83R6F75 — Amazon automated access blocked; star rating and review count require manual lookup before updating Review Strength score. Review Strength=1: only 2 reviews at time of scoring (repo data, 2026-06-22). Amazon URL confirmed: amazon.com/dp/B0F83R6F75 — automated fetch blocked; verify rating/count manually before next refresh Value for Money forced to 4 by Tim (June 2026) — consistent with other Chongker product family scores. See Product_Feature_Score_Details.xlsx for rationale. TACTILE COMFORT REVIEW (2026-07-01): Considered for reclassification from MateCat tier (5) to Percy tier (4) alongside other Chongker Tactile Comfort changes. Manufacturer/Amazon listing describes cloud-like softness, silicone 'toe beans', and seamless ultra-soft faux fur construction with no competing hard internal mechanisms (no sensors/movement hardware, unlike Percy/MateCat robotic lines) — tactile comfort is the product's primary marketed feature. No independent (non-manufacturer) reviews found directly comparing its fur/feel against MateCat or Percy. Tim confirmed keeping this at 5 (MateCat tier) based on this evidence. DEMENTIA SUITABILITY EVIDENCE TIER (2026-07-02): Tier C — dementia-suitability claims found only on Chongker's own marketing pages (unverified consultant/specialist quotes, no named institution); no independent research located. Capped at 4 per Tim's directive. Note: product complexity (voice commands, sleep-mode cycling, battery-status alerts on some models) also weighs against the Simplicity sub-criterion. Score is provisional pending dementia consultant review. DEMENTIA SUITABILITY RECALCULATED (2026-07-02, Tim-directed methodology): Simplicity=4, Familiar Form=3, Safety=4, Calmness=avg(Sound=4, Behavioral Realism=1)=2.5. Raw average of 4 sub-criteria=3.38, rounded=3, Evidence Tier C cap=4 -&gt; Final=3 (no change). This is a first-pass 'best effort' score pending dementia care consultant review (consultant search in progress as of 2026-07-02). Products in the 'Ai &amp; Robotic Pets' Type category are excluded from memory-care-relevant Best For lists via a separate Type filter in the Best For Weighting Table, independent of this score.</t>
         </is>
       </c>
     </row>
@@ -1225,7 +1224,7 @@
       </c>
       <c r="R11" s="7" t="inlineStr">
         <is>
-          <t>Breathing-only mechanism; no sensors, voice, or touch response. Sound Quality=1 and Sound Level Control=1 — product produces no sounds; scores reflect absence of any sound output (lowest possible score on both scales). Autonomous Interaction=3: breathing runs continuously without user direction. Review strength estimated; recommend manual verification. Black/white coat: high contrast, distinctive visibility. Product name updated: 'Original Black and White Shorthair Cat' per repo. Review Strength=4: 1200 reviews, 4.4★ (repo, 2026-06-22). SOUND QUALITY FLAG: With budget barking dogs=1 and Joy for All=3, Perfect Petzzz (no sounds at all) may need reconsideration — currently 1 pending Tim review.</t>
+          <t>Breathing-only mechanism; no sensors, voice, or touch response. Sound Level Control=1 — no on/off switch or mute (battery must be removed to silence). Autonomous Interaction=3: breathing runs continuously without user direction. Review strength estimated; recommend manual verification. Black/white coat: high contrast, distinctive visibility. Product name updated: 'Original Black and White Shorthair Cat' per repo. Review Strength=4: 1200 reviews, 4.4★ (repo, 2026-06-22). SOUND QUALITY UPDATE (2026-07-01, Tim-confirmed): Perfect Petzzz is NOT silent — manufacturer FAQ confirms the breathing mechanism emits sound as normal operation, and multiple Amazon reviews describe a mechanical/grinding noise rather than a soothing breath. Sound Quality rescored from 2 to 2 under the new merged rubric (was previously scored under 'absence of sound = neutral' logic, now scored on actual sound character; net score unchanged at 2, but rationale corrected). Sound appears to vary unit to unit per manufacturer's own FAQ and mixed review reports (some units near-silent/subtle snore, others audibly grinding) — no per-unit review data available to differentiate individual SKUs, so all 8 Perfect Petzzz products scored uniformly at 2 pending any future unit-specific verification. DEMENTIA SUITABILITY EVIDENCE TIER (2026-07-02): Tier D — no dementia-specific evidence found (independent or manufacturer); score reflects general sub-criteria judgment only (simplicity, familiar form, calmness, safety). Capped at 3. Score is provisional pending dementia consultant review. DEMENTIA SUITABILITY RECALCULATED (2026-07-02, Tim-directed methodology): Simplicity=5, Familiar Form=4, Safety=5, Calmness=avg(Sound=2, Behavioral Realism=1)=1.5. Raw average of 4 sub-criteria=3.88, rounded=4, Evidence Tier D cap=3 -&gt; Final=3 (no change). This is a first-pass 'best effort' score pending dementia care consultant review (consultant search in progress as of 2026-07-02). Products in the 'Ai &amp; Robotic Pets' Type category are excluded from memory-care-relevant Best For lists via a separate Type filter in the Best For Weighting Table, independent of this score.</t>
         </is>
       </c>
     </row>
@@ -1291,7 +1290,7 @@
       </c>
       <c r="R12" s="11" t="inlineStr">
         <is>
-          <t>Breathing-only mechanism; no sensors, voice, or touch response. Sound Quality=1 and Sound Level Control=1 — product produces no sounds; scores reflect absence of any sound output (lowest possible score on both scales). Autonomous Interaction=3: breathing runs continuously without user direction. Review strength estimated; recommend manual verification. Product name updated: 'Original Beagle' per repo. Review Strength=3: 466 reviews, 4.4★ (repo, 2026-06-22). SOUND QUALITY FLAG: With budget barking dogs=1 and Joy for All=3, Perfect Petzzz (no sounds at all) may need reconsideration — currently 1 pending Tim review.</t>
+          <t>Breathing-only mechanism; no sensors, voice, or touch response. Sound Level Control=1 — no on/off switch or mute (battery must be removed to silence). Autonomous Interaction=3: breathing runs continuously without user direction. Review strength estimated; recommend manual verification. Product name updated: 'Original Beagle' per repo. Review Strength=3: 466 reviews, 4.4★ (repo, 2026-06-22). SOUND QUALITY UPDATE (2026-07-01, Tim-confirmed): Perfect Petzzz is NOT silent — manufacturer FAQ confirms the breathing mechanism emits sound as normal operation, and multiple Amazon reviews describe a mechanical/grinding noise rather than a soothing breath. Sound Quality rescored from 2 to 2 under the new merged rubric (was previously scored under 'absence of sound = neutral' logic, now scored on actual sound character; net score unchanged at 2, but rationale corrected). Sound appears to vary unit to unit per manufacturer's own FAQ and mixed review reports (some units near-silent/subtle snore, others audibly grinding) — no per-unit review data available to differentiate individual SKUs, so all 8 Perfect Petzzz products scored uniformly at 2 pending any future unit-specific verification. DEMENTIA SUITABILITY EVIDENCE TIER (2026-07-02): Tier D — no dementia-specific evidence found (independent or manufacturer); score reflects general sub-criteria judgment only (simplicity, familiar form, calmness, safety). Capped at 3. Score is provisional pending dementia consultant review. DEMENTIA SUITABILITY RECALCULATED (2026-07-02, Tim-directed methodology): Simplicity=5, Familiar Form=4, Safety=5, Calmness=avg(Sound=2, Behavioral Realism=1)=1.5. Raw average of 4 sub-criteria=3.88, rounded=4, Evidence Tier D cap=3 -&gt; Final=3 (no change). This is a first-pass 'best effort' score pending dementia care consultant review (consultant search in progress as of 2026-07-02). Products in the 'Ai &amp; Robotic Pets' Type category are excluded from memory-care-relevant Best For lists via a separate Type filter in the Best For Weighting Table, independent of this score.</t>
         </is>
       </c>
     </row>
@@ -1357,7 +1356,7 @@
       </c>
       <c r="R13" s="7" t="inlineStr">
         <is>
-          <t>Hasbro 2023 'Hey Furby' — 25th anniversary edition. No app, no WiFi, no Bluetooth confirmed (Official Furby Wiki; IEEE Spectrum). 4x AA batteries. 5 voice-activated modes, 600+ pre-programmed reactions. Sound Level Control=2: no volume adjustment available (documented consumer complaint); only shutdown or mode switching. Brand=5: Hasbro, globally established, 58M+ units sold over 25 years. Review Strength=5: massive lifetime Amazon review volume. Dementia=2: loud/unpredictable, fantastical non-animal appearance — not recommended for memory care. Privacy=5: confirmed no wireless connectivity in 2023 model. IMPORTANT: DJ Furby (2025) is a different model from the Furby 2023 originally scored — elongated 'long oddbody' form factor with DJ/music theme (per Official Furby Wiki). Core feature scores carried over from 2023 Furby as closest available data; verify DJ-specific features (music modes, controls, form factor) before publishing. Review Strength=4: 772 reviews, 4.8★ (repo data, 2026-06-22). Visual contrast likely higher than regular Furby due to distinctive elongated DJ styling.</t>
+          <t>Hasbro 2023 'Hey Furby' — 25th anniversary edition. No app, no WiFi, no Bluetooth confirmed (Official Furby Wiki; IEEE Spectrum). 4x AA batteries. 5 voice-activated modes, 600+ pre-programmed reactions. Sound Level Control=2: no volume adjustment available (documented consumer complaint); only shutdown or mode switching. Brand=5: Hasbro, globally established, 58M+ units sold over 25 years. Review Strength=5: massive lifetime Amazon review volume. Dementia=2: loud/unpredictable, fantastical non-animal appearance — not recommended for memory care. Privacy=5: confirmed no wireless connectivity in 2023 model. IMPORTANT: DJ Furby (2025) is a different model from the Furby 2023 originally scored — elongated 'long oddbody' form factor with DJ/music theme (per Official Furby Wiki). Core feature scores carried over from 2023 Furby as closest available data; verify DJ-specific features (music modes, controls, form factor) before publishing. Review Strength=4: 772 reviews, 4.8★ (repo data, 2026-06-22). Visual contrast likely higher than regular Furby due to distinctive elongated DJ styling. DEMENTIA SUITABILITY EVIDENCE TIER (2026-07-02): Tier D — no dementia-specific evidence found (independent or manufacturer); score reflects general sub-criteria judgment only (simplicity, familiar form, calmness, safety). Capped at 3. Score is provisional pending dementia consultant review. DEMENTIA SUITABILITY RECALCULATED (2026-07-02, Tim-directed methodology): Simplicity=4, Familiar Form=3, Safety=5, Calmness=avg(Sound=3, Behavioral Realism=3)=3.0. Raw average of 4 sub-criteria=3.75, rounded=4, Evidence Tier D cap=3 -&gt; Final=3 (was 2). This is a first-pass 'best effort' score pending dementia care consultant review (consultant search in progress as of 2026-07-02). Products in the 'Ai &amp; Robotic Pets' Type category are excluded from memory-care-relevant Best For lists via a separate Type filter in the Best For Weighting Table, independent of this score.</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1422,7 @@
       </c>
       <c r="R14" s="11" t="inlineStr">
         <is>
-          <t>Founded 2022; CES 2025 debut; Series A1 funded (Beijing AI Industry Investment Fund). Privacy=3: local offline AI for daily use; photo uploads encrypted on-device before cloud (ropetai.com). 39°C bionic warmth feature unique in this market (verified Amazon B0GTPZ4N4M). Stationary desktop companion — no locomotion (Movement=1). Brand Reliability=3: legitimate but newer; 30-day returns per manufacturer. Review strength=3: growing — recommend re-check as product matures. Review Strength=2: 17 reviews, 4.3★ (repo data, 2026-06-22).</t>
+          <t>Founded 2022; CES 2025 debut; Series A1 funded (Beijing AI Industry Investment Fund). Privacy=3: local offline AI for daily use; photo uploads encrypted on-device before cloud (ropetai.com). 39°C bionic warmth feature unique in this market (verified Amazon B0GTPZ4N4M). Stationary desktop companion — no locomotion (Movement=1). Brand Reliability=3: legitimate but newer; 30-day returns per manufacturer. Review strength=3: growing — recommend re-check as product matures. Review Strength=2: 17 reviews, 4.3★ (repo data, 2026-06-22). DEMENTIA SUITABILITY EVIDENCE TIER (2026-07-02): Tier D — no dementia-specific evidence found (independent or manufacturer); score reflects general sub-criteria judgment only (simplicity, familiar form, calmness, safety). Capped at 3. Score is provisional pending dementia consultant review. DEMENTIA SUITABILITY RECALCULATED (2026-07-02, Tim-directed methodology): Simplicity=3, Familiar Form=2, Safety=4, Calmness=avg(Sound=3, Behavioral Realism=2)=2.5. Raw average of 4 sub-criteria=2.88, rounded=3, Evidence Tier D cap=3 -&gt; Final=3 (no change). This is a first-pass 'best effort' score pending dementia care consultant review (consultant search in progress as of 2026-07-02). Products in the 'Ai &amp; Robotic Pets' Type category are excluded from memory-care-relevant Best For lists via a separate Type filter in the Best For Weighting Table, independent of this score.</t>
         </is>
       </c>
     </row>
@@ -1489,7 +1488,7 @@
       </c>
       <c r="R15" s="7" t="inlineStr">
         <is>
-          <t>WARNING — LOW CONFIDENCE ACROSS ALL SCORES. No verified independent reviews found; all scores based on wuffyrobot.com marketing claims only. Review Strength=1: no verifiable third-party reviews identified. Brand Reliability=2: new/unverifiable brand, no established track record. Return/Gift Suitability=2: return policy unclear from DTC site. Recommend independent verification of product claims before featuring on site. Compare against Puppy Milow profile for scam-risk indicators. Review Strength=2: 80 reviews but only 3★ (repo data, 2026-06-22). Low rating confirms earlier caution flag about product quality/marketing claims.</t>
+          <t>WARNING — LOW CONFIDENCE ACROSS ALL SCORES. No verified independent reviews found; all scores based on wuffyrobot.com marketing claims only. Review Strength=1: no verifiable third-party reviews identified. Brand Reliability=2: new/unverifiable brand, no established track record. Return/Gift Suitability=2: return policy unclear from DTC site. Recommend independent verification of product claims before featuring on site. Compare against Puppy Milow profile for scam-risk indicators. Review Strength=2: 80 reviews but only 3★ (repo data, 2026-06-22). Low rating confirms earlier caution flag about product quality/marketing claims. DEMENTIA SUITABILITY EVIDENCE TIER (2026-07-02): Tier D — no dementia-specific evidence found (independent or manufacturer); score reflects general sub-criteria judgment only (simplicity, familiar form, calmness, safety). Capped at 3. Score is provisional pending dementia consultant review. DEMENTIA SUITABILITY RECALCULATED (2026-07-02, Tim-directed methodology): Simplicity=3, Familiar Form=3, Safety=4, Calmness=avg(Sound=2, Behavioral Realism=2)=2.0. Raw average of 4 sub-criteria=3.0, rounded=3, Evidence Tier D cap=3 -&gt; Final=3 (was 2). This is a first-pass 'best effort' score pending dementia care consultant review (consultant search in progress as of 2026-07-02). Products in the 'Ai &amp; Robotic Pets' Type category are excluded from memory-care-relevant Best For lists via a separate Type filter in the Best For Weighting Table, independent of this score.</t>
         </is>
       </c>
     </row>
@@ -1555,7 +1554,7 @@
       </c>
       <c r="R16" s="11" t="inlineStr">
         <is>
-          <t>Children's programmable toy robot dog with remote/gesture control. No WiFi or app required (infrared remote — Privacy=5). Hard plastic ABS shell, LED facial expressions, walks/spins/dances. 30-day returns, 90-day warranty per Amazon listing (B0FLXCXPHD). Sound Level Control=2: no volume adjustment noted; on/off states only. Dementia=1: remote-controlled, LED face, not a calming companion product. Not recommended for senior care use cases. Review Strength=3: 283 reviews, 4.4★ (repo data, 2026-06-22).</t>
+          <t>Children's programmable toy robot dog with remote/gesture control. No WiFi or app required (infrared remote — Privacy=5). Hard plastic ABS shell, LED facial expressions, walks/spins/dances. 30-day returns, 90-day warranty per Amazon listing (B0FLXCXPHD). Sound Level Control=2: no volume adjustment noted; on/off states only. Dementia=1: remote-controlled, LED face, not a calming companion product. Not recommended for senior care use cases. Review Strength=3: 283 reviews, 4.4★ (repo data, 2026-06-22). DEMENTIA SUITABILITY EVIDENCE TIER (2026-07-02): Tier D — no dementia-specific evidence found (independent or manufacturer); score reflects general sub-criteria judgment only (simplicity, familiar form, calmness, safety). Capped at 3. Score is provisional pending dementia consultant review. DEMENTIA SUITABILITY RECALCULATED (2026-07-02, Tim-directed methodology): Simplicity=3, Familiar Form=3, Safety=3, Calmness=avg(Sound=2, Behavioral Realism=2)=2.0. Raw average of 4 sub-criteria=2.75, rounded=3, Evidence Tier D cap=3 -&gt; Final=3 (was 1). This is a first-pass 'best effort' score pending dementia care consultant review (consultant search in progress as of 2026-07-02). Products in the 'Ai &amp; Robotic Pets' Type category are excluded from memory-care-relevant Best For lists via a separate Type filter in the Best For Weighting Table, independent of this score.</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1620,7 @@
       </c>
       <c r="R17" s="7" t="inlineStr">
         <is>
-          <t>KEYi Tech Loona. Rubric anchor product: Control Accessibility=1 (worst) and Customization Options=5 (best). ChatGPT-4o integration. Camera, WiFi, app, account all required. Camera=yes, Internet Access=yes per Product Matrix. Voice=4: excellent AI voice response but conversational not animal-mimicry. Not recommended for seniors or dementia care. Review Strength=4: 1,199 reviews, 4.2★ (repo data, 2026-06-22).</t>
+          <t>KEYi Tech Loona. Rubric anchor product: Control Accessibility=1 (worst) and Customization Options=5 (best). ChatGPT-4o integration. Camera, WiFi, app, account all required. Camera=yes, Internet Access=yes per Product Matrix. Voice=4: excellent AI voice response but conversational not animal-mimicry. Not recommended for seniors or dementia care. Review Strength=4: 1,199 reviews, 4.2★ (repo data, 2026-06-22). DEMENTIA SUITABILITY EVIDENCE TIER (2026-07-02): Tier D — no dementia-specific evidence found (independent or manufacturer); score reflects general sub-criteria judgment only (simplicity, familiar form, calmness, safety). Capped at 3. Score is provisional pending dementia consultant review. DEMENTIA SUITABILITY RECALCULATED (2026-07-02, Tim-directed methodology): Simplicity=1, Familiar Form=2, Safety=2, Calmness=avg(Sound=3, Behavioral Realism=2)=2.5. Raw average of 4 sub-criteria=1.88, rounded=2, Evidence Tier D cap=3 -&gt; Final=2 (was 1). This is a first-pass 'best effort' score pending dementia care consultant review (consultant search in progress as of 2026-07-02). Products in the 'Ai &amp; Robotic Pets' Type category are excluded from memory-care-relevant Best For lists via a separate Type filter in the Best For Weighting Table, independent of this score.</t>
         </is>
       </c>
     </row>
@@ -1687,7 +1686,7 @@
       </c>
       <c r="R18" s="11" t="inlineStr">
         <is>
-          <t>Camera=yes, Internet Access=yes per Product Matrix. Hard-shell rolling security camera robot; not a companion pet. Scores are category-level; minor spec differences between models noted. Review strength and Value estimated — recommend manual Amazon verification. Air 2 Plus has AI chat mode — highest AI tier in Enabot lineup per manufacturer. Product renamed to 'EBO Air 2 Plus FamilyBot'. Review Strength=3: 42 reviews, 5★ (repo data, 2026-06-22).</t>
+          <t>Camera=yes, Internet Access=yes per Product Matrix. Hard-shell rolling security camera robot; not a companion pet. Scores are category-level; minor spec differences between models noted. Review strength and Value estimated — recommend manual Amazon verification. Air 2 Plus has AI chat mode — highest AI tier in Enabot lineup per manufacturer. Product renamed to 'EBO Air 2 Plus FamilyBot'. Review Strength=3: 42 reviews, 5★ (repo data, 2026-06-22). DEMENTIA SUITABILITY EVIDENCE TIER (2026-07-02): Tier D — no dementia-specific evidence found (independent or manufacturer); score reflects general sub-criteria judgment only (simplicity, familiar form, calmness, safety). Capped at 3. Score is provisional pending dementia consultant review. DEMENTIA SUITABILITY RECALCULATED (2026-07-02, Tim-directed methodology): Simplicity=2, Familiar Form=1, Safety=2, Calmness=avg(Sound=3, Behavioral Realism=1)=2.0. Raw average of 4 sub-criteria=1.75, rounded=2, Evidence Tier D cap=3 -&gt; Final=2 (was 1). This is a first-pass 'best effort' score pending dementia care consultant review (consultant search in progress as of 2026-07-02). Products in the 'Ai &amp; Robotic Pets' Type category are excluded from memory-care-relevant Best For lists via a separate Type filter in the Best For Weighting Table, independent of this score.</t>
         </is>
       </c>
     </row>
@@ -1753,7 +1752,7 @@
       </c>
       <c r="R19" s="7" t="inlineStr">
         <is>
-          <t>Camera=yes, Internet Access=yes per Product Matrix. Hard-shell rolling security camera robot; not a companion pet. Scores are category-level; minor spec differences between models noted. Review strength and Value estimated — recommend manual Amazon verification. Product renamed in repo to 'EBO Air 2 FamilyBot'. Review Strength=3: 72 reviews, 4.5★ (repo data, 2026-06-22).</t>
+          <t>Camera=yes, Internet Access=yes per Product Matrix. Hard-shell rolling security camera robot; not a companion pet. Scores are category-level; minor spec differences between models noted. Review strength and Value estimated — recommend manual Amazon verification. Product renamed in repo to 'EBO Air 2 FamilyBot'. Review Strength=3: 72 reviews, 4.5★ (repo data, 2026-06-22). DEMENTIA SUITABILITY EVIDENCE TIER (2026-07-02): Tier D — no dementia-specific evidence found (independent or manufacturer); score reflects general sub-criteria judgment only (simplicity, familiar form, calmness, safety). Capped at 3. Score is provisional pending dementia consultant review. DEMENTIA SUITABILITY RECALCULATED (2026-07-02, Tim-directed methodology): Simplicity=2, Familiar Form=1, Safety=2, Calmness=avg(Sound=3, Behavioral Realism=1)=2.0. Raw average of 4 sub-criteria=1.75, rounded=2, Evidence Tier D cap=3 -&gt; Final=2 (was 1). This is a first-pass 'best effort' score pending dementia care consultant review (consultant search in progress as of 2026-07-02). Products in the 'Ai &amp; Robotic Pets' Type category are excluded from memory-care-relevant Best For lists via a separate Type filter in the Best For Weighting Table, independent of this score.</t>
         </is>
       </c>
     </row>
@@ -1811,7 +1810,7 @@
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>Animal</t>
+          <t>Category</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -1857,7 +1856,7 @@
         </is>
       </c>
       <c r="E3" s="19" t="n">
-        <v>4.4</v>
+        <v>4.25</v>
       </c>
       <c r="F3" s="19" t="n">
         <v>4.5</v>
@@ -1869,7 +1868,7 @@
       </c>
       <c r="H3" s="19" t="inlineStr">
         <is>
-          <t>score=4.40 rating=4.5</t>
+          <t>score=4.25 rating=4.5</t>
         </is>
       </c>
     </row>
@@ -1895,7 +1894,7 @@
         </is>
       </c>
       <c r="E4" s="20" t="n">
-        <v>4.4</v>
+        <v>4.25</v>
       </c>
       <c r="F4" s="20" t="n">
         <v>4.5</v>
@@ -1907,7 +1906,7 @@
       </c>
       <c r="H4" s="20" t="inlineStr">
         <is>
-          <t>score=4.40 rating=4.5</t>
+          <t>score=4.25 rating=4.5</t>
         </is>
       </c>
     </row>
@@ -1933,7 +1932,7 @@
         </is>
       </c>
       <c r="E5" s="19" t="n">
-        <v>4.4</v>
+        <v>4.25</v>
       </c>
       <c r="F5" s="19" t="n">
         <v>4.3</v>
@@ -1945,7 +1944,7 @@
       </c>
       <c r="H5" s="19" t="inlineStr">
         <is>
-          <t>score=4.40 rating=4.3</t>
+          <t>score=4.25 rating=4.3</t>
         </is>
       </c>
     </row>
@@ -1971,7 +1970,7 @@
         </is>
       </c>
       <c r="E6" s="20" t="n">
-        <v>4.35</v>
+        <v>4.2</v>
       </c>
       <c r="F6" s="20" t="n">
         <v>5</v>
@@ -1983,7 +1982,7 @@
       </c>
       <c r="H6" s="20" t="inlineStr">
         <is>
-          <t>score=4.35 rating=5</t>
+          <t>score=4.20 rating=5</t>
         </is>
       </c>
     </row>

--- a/Documentation/Best For Lists/Best for Seniors Living Alone List.xlsx
+++ b/Documentation/Best For Lists/Best for Seniors Living Alone List.xlsx
@@ -195,10 +195,10 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -588,7 +588,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R19"/>
+  <dimension ref="A1:R20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -621,7 +621,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-07-02  |  Products shown: 15  |  Eliminated by dedup rule: 14</t>
+          <t>Generated: 2026-07-07  |  Products shown: 16  |  Eliminated by dedup rule: 13</t>
         </is>
       </c>
     </row>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="C11" s="7" t="inlineStr">
         <is>
-          <t>Original Black and White Shorthair Cat</t>
+          <t>Grey Tabby Cat</t>
         </is>
       </c>
       <c r="D11" s="8" t="inlineStr">
@@ -1190,10 +1190,10 @@
         <v>44.45</v>
       </c>
       <c r="G11" s="8" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="H11" s="8" t="n">
-        <v>1200</v>
+        <v>848</v>
       </c>
       <c r="I11" s="15" t="n">
         <v>3.75</v>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="R11" s="7" t="inlineStr">
         <is>
-          <t>Breathing-only mechanism; no sensors, voice, or touch response. Sound Level Control=1 — no on/off switch or mute (battery must be removed to silence). Autonomous Interaction=3: breathing runs continuously without user direction. Review strength estimated; recommend manual verification. Black/white coat: high contrast, distinctive visibility. Product name updated: 'Original Black and White Shorthair Cat' per repo. Review Strength=4: 1200 reviews, 4.4★ (repo, 2026-06-22). SOUND QUALITY UPDATE (2026-07-01, Tim-confirmed): Perfect Petzzz is NOT silent — manufacturer FAQ confirms the breathing mechanism emits sound as normal operation, and multiple Amazon reviews describe a mechanical/grinding noise rather than a soothing breath. Sound Quality rescored from 2 to 2 under the new merged rubric (was previously scored under 'absence of sound = neutral' logic, now scored on actual sound character; net score unchanged at 2, but rationale corrected). Sound appears to vary unit to unit per manufacturer's own FAQ and mixed review reports (some units near-silent/subtle snore, others audibly grinding) — no per-unit review data available to differentiate individual SKUs, so all 8 Perfect Petzzz products scored uniformly at 2 pending any future unit-specific verification. DEMENTIA SUITABILITY EVIDENCE TIER (2026-07-02): Tier D — no dementia-specific evidence found (independent or manufacturer); score reflects general sub-criteria judgment only (simplicity, familiar form, calmness, safety). Capped at 3. Score is provisional pending dementia consultant review. DEMENTIA SUITABILITY RECALCULATED (2026-07-02, Tim-directed methodology): Simplicity=5, Familiar Form=4, Safety=5, Calmness=avg(Sound=2, Behavioral Realism=1)=1.5. Raw average of 4 sub-criteria=3.88, rounded=4, Evidence Tier D cap=3 -&gt; Final=3 (no change). This is a first-pass 'best effort' score pending dementia care consultant review (consultant search in progress as of 2026-07-02). Products in the 'Ai &amp; Robotic Pets' Type category are excluded from memory-care-relevant Best For lists via a separate Type filter in the Best For Weighting Table, independent of this score.</t>
+          <t>Breathing-only mechanism; no sensors, voice, or touch response. Sound Level Control=1 — no on/off switch or mute (battery must be removed to silence). Autonomous Interaction=3: breathing runs continuously without user direction. Review strength estimated; recommend manual verification. Previously scored as 'Calico Cat' — now matched to 'Grey Tabby Cat' per repo. Verify this is the correct product match before publishing. Review Strength=4: 848 reviews, 4.3★ (repo data, 2026-06-22). SOUND QUALITY UPDATE (2026-07-01, Tim-confirmed): Perfect Petzzz is NOT silent — manufacturer FAQ confirms the breathing mechanism emits sound as normal operation, and multiple Amazon reviews describe a mechanical/grinding noise rather than a soothing breath. Sound Quality rescored from 2 to 2 under the new merged rubric (was previously scored under 'absence of sound = neutral' logic, now scored on actual sound character; net score unchanged at 2, but rationale corrected). Sound appears to vary unit to unit per manufacturer's own FAQ and mixed review reports (some units near-silent/subtle snore, others audibly grinding) — no per-unit review data available to differentiate individual SKUs, so all 8 Perfect Petzzz products scored uniformly at 2 pending any future unit-specific verification. DEMENTIA SUITABILITY EVIDENCE TIER (2026-07-02): Tier D — no dementia-specific evidence found (independent or manufacturer); score reflects general sub-criteria judgment only (simplicity, familiar form, calmness, safety). Capped at 3. Score is provisional pending dementia consultant review. DEMENTIA SUITABILITY RECALCULATED (2026-07-02, Tim-directed methodology): Simplicity=5, Familiar Form=4, Safety=5, Calmness=avg(Sound=2, Behavioral Realism=1)=1.5. Raw average of 4 sub-criteria=3.88, rounded=4, Evidence Tier D cap=3 -&gt; Final=3 (no change). This is a first-pass 'best effort' score pending dementia care consultant review (consultant search in progress as of 2026-07-02). Products in the 'Ai &amp; Robotic Pets' Type category are excluded from memory-care-relevant Best For lists via a separate Type filter in the Best For Weighting Table, independent of this score.</t>
         </is>
       </c>
     </row>
@@ -1239,7 +1239,7 @@
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>Original Beagle</t>
+          <t>Original Chocolate Lab</t>
         </is>
       </c>
       <c r="D12" s="12" t="inlineStr">
@@ -1256,10 +1256,10 @@
         <v>44.45</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>466</v>
+        <v>553</v>
       </c>
       <c r="I12" s="14" t="n">
         <v>3.75</v>
@@ -1290,7 +1290,7 @@
       </c>
       <c r="R12" s="11" t="inlineStr">
         <is>
-          <t>Breathing-only mechanism; no sensors, voice, or touch response. Sound Level Control=1 — no on/off switch or mute (battery must be removed to silence). Autonomous Interaction=3: breathing runs continuously without user direction. Review strength estimated; recommend manual verification. Product name updated: 'Original Beagle' per repo. Review Strength=3: 466 reviews, 4.4★ (repo, 2026-06-22). SOUND QUALITY UPDATE (2026-07-01, Tim-confirmed): Perfect Petzzz is NOT silent — manufacturer FAQ confirms the breathing mechanism emits sound as normal operation, and multiple Amazon reviews describe a mechanical/grinding noise rather than a soothing breath. Sound Quality rescored from 2 to 2 under the new merged rubric (was previously scored under 'absence of sound = neutral' logic, now scored on actual sound character; net score unchanged at 2, but rationale corrected). Sound appears to vary unit to unit per manufacturer's own FAQ and mixed review reports (some units near-silent/subtle snore, others audibly grinding) — no per-unit review data available to differentiate individual SKUs, so all 8 Perfect Petzzz products scored uniformly at 2 pending any future unit-specific verification. DEMENTIA SUITABILITY EVIDENCE TIER (2026-07-02): Tier D — no dementia-specific evidence found (independent or manufacturer); score reflects general sub-criteria judgment only (simplicity, familiar form, calmness, safety). Capped at 3. Score is provisional pending dementia consultant review. DEMENTIA SUITABILITY RECALCULATED (2026-07-02, Tim-directed methodology): Simplicity=5, Familiar Form=4, Safety=5, Calmness=avg(Sound=2, Behavioral Realism=1)=1.5. Raw average of 4 sub-criteria=3.88, rounded=4, Evidence Tier D cap=3 -&gt; Final=3 (no change). This is a first-pass 'best effort' score pending dementia care consultant review (consultant search in progress as of 2026-07-02). Products in the 'Ai &amp; Robotic Pets' Type category are excluded from memory-care-relevant Best For lists via a separate Type filter in the Best For Weighting Table, independent of this score.</t>
+          <t>Breathing-only mechanism; no sensors, voice, or touch response. Sound Level Control=1 — no on/off switch or mute (battery must be removed to silence). Autonomous Interaction=3: breathing runs continuously without user direction. Review strength estimated; recommend manual verification. Product name updated: 'Original Chocolate Lab' per repo. Review Strength=4: 553 reviews, 4.3★ (repo, 2026-06-22). SOUND QUALITY UPDATE (2026-07-01, Tim-confirmed): Perfect Petzzz is NOT silent — manufacturer FAQ confirms the breathing mechanism emits sound as normal operation, and multiple Amazon reviews describe a mechanical/grinding noise rather than a soothing breath. Sound Quality rescored from 2 to 2 under the new merged rubric (was previously scored under 'absence of sound = neutral' logic, now scored on actual sound character; net score unchanged at 2, but rationale corrected). Sound appears to vary unit to unit per manufacturer's own FAQ and mixed review reports (some units near-silent/subtle snore, others audibly grinding) — no per-unit review data available to differentiate individual SKUs, so all 8 Perfect Petzzz products scored uniformly at 2 pending any future unit-specific verification. DEMENTIA SUITABILITY EVIDENCE TIER (2026-07-02): Tier D — no dementia-specific evidence found (independent or manufacturer); score reflects general sub-criteria judgment only (simplicity, familiar form, calmness, safety). Capped at 3. Score is provisional pending dementia consultant review. DEMENTIA SUITABILITY RECALCULATED (2026-07-02, Tim-directed methodology): Simplicity=5, Familiar Form=4, Safety=5, Calmness=avg(Sound=2, Behavioral Realism=1)=1.5. Raw average of 4 sub-criteria=3.88, rounded=4, Evidence Tier D cap=3 -&gt; Final=3 (no change). This is a first-pass 'best effort' score pending dementia care consultant review (consultant search in progress as of 2026-07-02). Products in the 'Ai &amp; Robotic Pets' Type category are excluded from memory-care-relevant Best For lists via a separate Type filter in the Best For Weighting Table, independent of this score.</t>
         </is>
       </c>
     </row>
@@ -1300,35 +1300,33 @@
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>Furby</t>
+          <t>Perfect Petzzz</t>
         </is>
       </c>
       <c r="C13" s="7" t="inlineStr">
         <is>
-          <t>DJ Furby</t>
+          <t>Original Black and White Shorthair Cat</t>
         </is>
       </c>
       <c r="D13" s="8" t="inlineStr">
         <is>
-          <t>Budget Friendly</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E13" s="8" t="inlineStr">
         <is>
-          <t>Robot</t>
-        </is>
-      </c>
-      <c r="F13" s="8" t="n">
-        <v>50.11</v>
-      </c>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F13" s="8" t="n"/>
       <c r="G13" s="8" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="H13" s="8" t="n">
-        <v>772</v>
+        <v>0</v>
       </c>
       <c r="I13" s="15" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="J13" s="8" t="n">
         <v>2</v>
@@ -1337,26 +1335,26 @@
         <v>3</v>
       </c>
       <c r="L13" s="8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M13" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N13" s="8" t="n">
         <v>5</v>
       </c>
       <c r="O13" s="8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P13" s="8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q13" s="8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R13" s="7" t="inlineStr">
         <is>
-          <t>Hasbro 2023 'Hey Furby' — 25th anniversary edition. No app, no WiFi, no Bluetooth confirmed (Official Furby Wiki; IEEE Spectrum). 4x AA batteries. 5 voice-activated modes, 600+ pre-programmed reactions. Sound Level Control=2: no volume adjustment available (documented consumer complaint); only shutdown or mode switching. Brand=5: Hasbro, globally established, 58M+ units sold over 25 years. Review Strength=5: massive lifetime Amazon review volume. Dementia=2: loud/unpredictable, fantastical non-animal appearance — not recommended for memory care. Privacy=5: confirmed no wireless connectivity in 2023 model. IMPORTANT: DJ Furby (2025) is a different model from the Furby 2023 originally scored — elongated 'long oddbody' form factor with DJ/music theme (per Official Furby Wiki). Core feature scores carried over from 2023 Furby as closest available data; verify DJ-specific features (music modes, controls, form factor) before publishing. Review Strength=4: 772 reviews, 4.8★ (repo data, 2026-06-22). Visual contrast likely higher than regular Furby due to distinctive elongated DJ styling. DEMENTIA SUITABILITY EVIDENCE TIER (2026-07-02): Tier D — no dementia-specific evidence found (independent or manufacturer); score reflects general sub-criteria judgment only (simplicity, familiar form, calmness, safety). Capped at 3. Score is provisional pending dementia consultant review. DEMENTIA SUITABILITY RECALCULATED (2026-07-02, Tim-directed methodology): Simplicity=4, Familiar Form=3, Safety=5, Calmness=avg(Sound=3, Behavioral Realism=3)=3.0. Raw average of 4 sub-criteria=3.75, rounded=4, Evidence Tier D cap=3 -&gt; Final=3 (was 2). This is a first-pass 'best effort' score pending dementia care consultant review (consultant search in progress as of 2026-07-02). Products in the 'Ai &amp; Robotic Pets' Type category are excluded from memory-care-relevant Best For lists via a separate Type filter in the Best For Weighting Table, independent of this score.</t>
+          <t>Breathing-only mechanism; no sensors, voice, or touch response. Sound Level Control=1 — no on/off switch or mute (battery must be removed to silence). Autonomous Interaction=3: breathing runs continuously without user direction. Review strength estimated; recommend manual verification. Black/white coat: high contrast, distinctive visibility. Product name updated: 'Original Black and White Shorthair Cat' per repo. Review Strength=4: 1200 reviews, 4.4★ (repo, 2026-06-22). SOUND QUALITY UPDATE (2026-07-01, Tim-confirmed): Perfect Petzzz is NOT silent — manufacturer FAQ confirms the breathing mechanism emits sound as normal operation, and multiple Amazon reviews describe a mechanical/grinding noise rather than a soothing breath. Sound Quality rescored from 2 to 2 under the new merged rubric (was previously scored under 'absence of sound = neutral' logic, now scored on actual sound character; net score unchanged at 2, but rationale corrected). Sound appears to vary unit to unit per manufacturer's own FAQ and mixed review reports (some units near-silent/subtle snore, others audibly grinding) — no per-unit review data available to differentiate individual SKUs, so all 8 Perfect Petzzz products scored uniformly at 2 pending any future unit-specific verification. DEMENTIA SUITABILITY EVIDENCE TIER (2026-07-02): Tier D — no dementia-specific evidence found (independent or manufacturer); score reflects general sub-criteria judgment only (simplicity, familiar form, calmness, safety). Capped at 3. Score is provisional pending dementia consultant review. DEMENTIA SUITABILITY RECALCULATED (2026-07-02, Tim-directed methodology): Simplicity=5, Familiar Form=4, Safety=5, Calmness=avg(Sound=2, Behavioral Realism=1)=1.5. Raw average of 4 sub-criteria=3.88, rounded=4, Evidence Tier D cap=3 -&gt; Final=3 (no change). This is a first-pass 'best effort' score pending dementia care consultant review (consultant search in progress as of 2026-07-02). Products in the 'Ai &amp; Robotic Pets' Type category are excluded from memory-care-relevant Best For lists via a separate Type filter in the Best For Weighting Table, independent of this score.</t>
         </is>
       </c>
     </row>
@@ -1366,17 +1364,17 @@
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>Ropet</t>
+          <t>Furby</t>
         </is>
       </c>
       <c r="C14" s="11" t="inlineStr">
         <is>
-          <t>KAMOMO</t>
+          <t>DJ Furby</t>
         </is>
       </c>
       <c r="D14" s="12" t="inlineStr">
         <is>
-          <t>Premium</t>
+          <t>Budget Friendly</t>
         </is>
       </c>
       <c r="E14" s="12" t="inlineStr">
@@ -1385,44 +1383,44 @@
         </is>
       </c>
       <c r="F14" s="12" t="n">
-        <v>349</v>
+        <v>50.11</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>17</v>
+        <v>772</v>
       </c>
       <c r="I14" s="14" t="n">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L14" s="12" t="n">
         <v>4</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N14" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O14" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P14" s="12" t="n">
         <v>4</v>
       </c>
       <c r="Q14" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R14" s="11" t="inlineStr">
         <is>
-          <t>Founded 2022; CES 2025 debut; Series A1 funded (Beijing AI Industry Investment Fund). Privacy=3: local offline AI for daily use; photo uploads encrypted on-device before cloud (ropetai.com). 39°C bionic warmth feature unique in this market (verified Amazon B0GTPZ4N4M). Stationary desktop companion — no locomotion (Movement=1). Brand Reliability=3: legitimate but newer; 30-day returns per manufacturer. Review strength=3: growing — recommend re-check as product matures. Review Strength=2: 17 reviews, 4.3★ (repo data, 2026-06-22). DEMENTIA SUITABILITY EVIDENCE TIER (2026-07-02): Tier D — no dementia-specific evidence found (independent or manufacturer); score reflects general sub-criteria judgment only (simplicity, familiar form, calmness, safety). Capped at 3. Score is provisional pending dementia consultant review. DEMENTIA SUITABILITY RECALCULATED (2026-07-02, Tim-directed methodology): Simplicity=3, Familiar Form=2, Safety=4, Calmness=avg(Sound=3, Behavioral Realism=2)=2.5. Raw average of 4 sub-criteria=2.88, rounded=3, Evidence Tier D cap=3 -&gt; Final=3 (no change). This is a first-pass 'best effort' score pending dementia care consultant review (consultant search in progress as of 2026-07-02). Products in the 'Ai &amp; Robotic Pets' Type category are excluded from memory-care-relevant Best For lists via a separate Type filter in the Best For Weighting Table, independent of this score.</t>
+          <t>Hasbro 2023 'Hey Furby' — 25th anniversary edition. No app, no WiFi, no Bluetooth confirmed (Official Furby Wiki; IEEE Spectrum). 4x AA batteries. 5 voice-activated modes, 600+ pre-programmed reactions. Sound Level Control=2: no volume adjustment available (documented consumer complaint); only shutdown or mode switching. Brand=5: Hasbro, globally established, 58M+ units sold over 25 years. Review Strength=5: massive lifetime Amazon review volume. Dementia=2: loud/unpredictable, fantastical non-animal appearance — not recommended for memory care. Privacy=5: confirmed no wireless connectivity in 2023 model. IMPORTANT: DJ Furby (2025) is a different model from the Furby 2023 originally scored — elongated 'long oddbody' form factor with DJ/music theme (per Official Furby Wiki). Core feature scores carried over from 2023 Furby as closest available data; verify DJ-specific features (music modes, controls, form factor) before publishing. Review Strength=4: 772 reviews, 4.8★ (repo data, 2026-06-22). Visual contrast likely higher than regular Furby due to distinctive elongated DJ styling. DEMENTIA SUITABILITY EVIDENCE TIER (2026-07-02): Tier D — no dementia-specific evidence found (independent or manufacturer); score reflects general sub-criteria judgment only (simplicity, familiar form, calmness, safety). Capped at 3. Score is provisional pending dementia consultant review. DEMENTIA SUITABILITY RECALCULATED (2026-07-02, Tim-directed methodology): Simplicity=4, Familiar Form=3, Safety=5, Calmness=avg(Sound=3, Behavioral Realism=3)=3.0. Raw average of 4 sub-criteria=3.75, rounded=4, Evidence Tier D cap=3 -&gt; Final=3 (was 2). This is a first-pass 'best effort' score pending dementia care consultant review (consultant search in progress as of 2026-07-02). Products in the 'Ai &amp; Robotic Pets' Type category are excluded from memory-care-relevant Best For lists via a separate Type filter in the Best For Weighting Table, independent of this score.</t>
         </is>
       </c>
     </row>
@@ -1432,44 +1430,44 @@
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>Wuffy</t>
+          <t>Ropet</t>
         </is>
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>Wuffy Robot Puppy</t>
+          <t>KAMOMO</t>
         </is>
       </c>
       <c r="D15" s="8" t="inlineStr">
         <is>
-          <t>Budget Friendly</t>
+          <t>Premium</t>
         </is>
       </c>
       <c r="E15" s="8" t="inlineStr">
         <is>
-          <t>Dog</t>
+          <t>Robot</t>
         </is>
       </c>
       <c r="F15" s="8" t="n">
-        <v>25.99</v>
+        <v>349</v>
       </c>
       <c r="G15" s="8" t="n">
-        <v>3</v>
+        <v>4.3</v>
       </c>
       <c r="H15" s="8" t="n">
-        <v>80</v>
-      </c>
-      <c r="I15" s="16" t="n">
-        <v>2.9</v>
+        <v>17</v>
+      </c>
+      <c r="I15" s="15" t="n">
+        <v>3.5</v>
       </c>
       <c r="J15" s="8" t="n">
         <v>3</v>
       </c>
       <c r="K15" s="8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L15" s="8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M15" s="8" t="n">
         <v>2</v>
@@ -1481,14 +1479,14 @@
         <v>3</v>
       </c>
       <c r="P15" s="8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q15" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R15" s="7" t="inlineStr">
         <is>
-          <t>WARNING — LOW CONFIDENCE ACROSS ALL SCORES. No verified independent reviews found; all scores based on wuffyrobot.com marketing claims only. Review Strength=1: no verifiable third-party reviews identified. Brand Reliability=2: new/unverifiable brand, no established track record. Return/Gift Suitability=2: return policy unclear from DTC site. Recommend independent verification of product claims before featuring on site. Compare against Puppy Milow profile for scam-risk indicators. Review Strength=2: 80 reviews but only 3★ (repo data, 2026-06-22). Low rating confirms earlier caution flag about product quality/marketing claims. DEMENTIA SUITABILITY EVIDENCE TIER (2026-07-02): Tier D — no dementia-specific evidence found (independent or manufacturer); score reflects general sub-criteria judgment only (simplicity, familiar form, calmness, safety). Capped at 3. Score is provisional pending dementia consultant review. DEMENTIA SUITABILITY RECALCULATED (2026-07-02, Tim-directed methodology): Simplicity=3, Familiar Form=3, Safety=4, Calmness=avg(Sound=2, Behavioral Realism=2)=2.0. Raw average of 4 sub-criteria=3.0, rounded=3, Evidence Tier D cap=3 -&gt; Final=3 (was 2). This is a first-pass 'best effort' score pending dementia care consultant review (consultant search in progress as of 2026-07-02). Products in the 'Ai &amp; Robotic Pets' Type category are excluded from memory-care-relevant Best For lists via a separate Type filter in the Best For Weighting Table, independent of this score.</t>
+          <t>Founded 2022; CES 2025 debut; Series A1 funded (Beijing AI Industry Investment Fund). Privacy=3: local offline AI for daily use; photo uploads encrypted on-device before cloud (ropetai.com). 39°C bionic warmth feature unique in this market (verified Amazon B0GTPZ4N4M). Stationary desktop companion — no locomotion (Movement=1). Brand Reliability=3: legitimate but newer; 30-day returns per manufacturer. Review strength=3: growing — recommend re-check as product matures. Review Strength=2: 17 reviews, 4.3★ (repo data, 2026-06-22). DEMENTIA SUITABILITY EVIDENCE TIER (2026-07-02): Tier D — no dementia-specific evidence found (independent or manufacturer); score reflects general sub-criteria judgment only (simplicity, familiar form, calmness, safety). Capped at 3. Score is provisional pending dementia consultant review. DEMENTIA SUITABILITY RECALCULATED (2026-07-02, Tim-directed methodology): Simplicity=3, Familiar Form=2, Safety=4, Calmness=avg(Sound=3, Behavioral Realism=2)=2.5. Raw average of 4 sub-criteria=2.88, rounded=3, Evidence Tier D cap=3 -&gt; Final=3 (no change). This is a first-pass 'best effort' score pending dementia care consultant review (consultant search in progress as of 2026-07-02). Products in the 'Ai &amp; Robotic Pets' Type category are excluded from memory-care-relevant Best For lists via a separate Type filter in the Best For Weighting Table, independent of this score.</t>
         </is>
       </c>
     </row>
@@ -1498,12 +1496,12 @@
       </c>
       <c r="B16" s="11" t="inlineStr">
         <is>
-          <t>Ruko</t>
+          <t>Wuffy</t>
         </is>
       </c>
       <c r="C16" s="11" t="inlineStr">
         <is>
-          <t>18011 Smart Robot Dog</t>
+          <t>Wuffy Robot Puppy</t>
         </is>
       </c>
       <c r="D16" s="12" t="inlineStr">
@@ -1517,44 +1515,44 @@
         </is>
       </c>
       <c r="F16" s="12" t="n">
-        <v>69.98999999999999</v>
+        <v>25.99</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>4.4</v>
+        <v>3</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>283</v>
-      </c>
-      <c r="I16" s="17" t="n">
-        <v>2.6</v>
+        <v>80</v>
+      </c>
+      <c r="I16" s="16" t="n">
+        <v>2.9</v>
       </c>
       <c r="J16" s="12" t="n">
         <v>3</v>
       </c>
       <c r="K16" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M16" s="12" t="n">
         <v>2</v>
       </c>
       <c r="N16" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O16" s="12" t="n">
         <v>3</v>
       </c>
       <c r="P16" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q16" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="Q16" s="12" t="n">
-        <v>3</v>
-      </c>
       <c r="R16" s="11" t="inlineStr">
         <is>
-          <t>Children's programmable toy robot dog with remote/gesture control. No WiFi or app required (infrared remote — Privacy=5). Hard plastic ABS shell, LED facial expressions, walks/spins/dances. 30-day returns, 90-day warranty per Amazon listing (B0FLXCXPHD). Sound Level Control=2: no volume adjustment noted; on/off states only. Dementia=1: remote-controlled, LED face, not a calming companion product. Not recommended for senior care use cases. Review Strength=3: 283 reviews, 4.4★ (repo data, 2026-06-22). DEMENTIA SUITABILITY EVIDENCE TIER (2026-07-02): Tier D — no dementia-specific evidence found (independent or manufacturer); score reflects general sub-criteria judgment only (simplicity, familiar form, calmness, safety). Capped at 3. Score is provisional pending dementia consultant review. DEMENTIA SUITABILITY RECALCULATED (2026-07-02, Tim-directed methodology): Simplicity=3, Familiar Form=3, Safety=3, Calmness=avg(Sound=2, Behavioral Realism=2)=2.0. Raw average of 4 sub-criteria=2.75, rounded=3, Evidence Tier D cap=3 -&gt; Final=3 (was 1). This is a first-pass 'best effort' score pending dementia care consultant review (consultant search in progress as of 2026-07-02). Products in the 'Ai &amp; Robotic Pets' Type category are excluded from memory-care-relevant Best For lists via a separate Type filter in the Best For Weighting Table, independent of this score.</t>
+          <t>WARNING — LOW CONFIDENCE ACROSS ALL SCORES. No verified independent reviews found; all scores based on wuffyrobot.com marketing claims only. Review Strength=1: no verifiable third-party reviews identified. Brand Reliability=2: new/unverifiable brand, no established track record. Return/Gift Suitability=2: return policy unclear from DTC site. Recommend independent verification of product claims before featuring on site. Compare against Puppy Milow profile for scam-risk indicators. Review Strength=2: 80 reviews but only 3★ (repo data, 2026-06-22). Low rating confirms earlier caution flag about product quality/marketing claims. DEMENTIA SUITABILITY EVIDENCE TIER (2026-07-02): Tier D — no dementia-specific evidence found (independent or manufacturer); score reflects general sub-criteria judgment only (simplicity, familiar form, calmness, safety). Capped at 3. Score is provisional pending dementia consultant review. DEMENTIA SUITABILITY RECALCULATED (2026-07-02, Tim-directed methodology): Simplicity=3, Familiar Form=3, Safety=4, Calmness=avg(Sound=2, Behavioral Realism=2)=2.0. Raw average of 4 sub-criteria=3.0, rounded=3, Evidence Tier D cap=3 -&gt; Final=3 (was 2). This is a first-pass 'best effort' score pending dementia care consultant review (consultant search in progress as of 2026-07-02). Products in the 'Ai &amp; Robotic Pets' Type category are excluded from memory-care-relevant Best For lists via a separate Type filter in the Best For Weighting Table, independent of this score.</t>
         </is>
       </c>
     </row>
@@ -1564,17 +1562,17 @@
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>Loona</t>
+          <t>Ruko</t>
         </is>
       </c>
       <c r="C17" s="7" t="inlineStr">
         <is>
-          <t>Robot Pet Dog</t>
+          <t>18011 Smart Robot Dog</t>
         </is>
       </c>
       <c r="D17" s="8" t="inlineStr">
         <is>
-          <t>Premium</t>
+          <t>Budget Friendly</t>
         </is>
       </c>
       <c r="E17" s="8" t="inlineStr">
@@ -1583,34 +1581,34 @@
         </is>
       </c>
       <c r="F17" s="8" t="n">
-        <v>499</v>
+        <v>69.98999999999999</v>
       </c>
       <c r="G17" s="8" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="H17" s="8" t="n">
-        <v>1199</v>
-      </c>
-      <c r="I17" s="16" t="n">
-        <v>2.35</v>
+        <v>283</v>
+      </c>
+      <c r="I17" s="17" t="n">
+        <v>2.6</v>
       </c>
       <c r="J17" s="8" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K17" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L17" s="8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M17" s="8" t="n">
         <v>2</v>
       </c>
       <c r="N17" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O17" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P17" s="8" t="n">
         <v>2</v>
@@ -1620,7 +1618,7 @@
       </c>
       <c r="R17" s="7" t="inlineStr">
         <is>
-          <t>KEYi Tech Loona. Rubric anchor product: Control Accessibility=1 (worst) and Customization Options=5 (best). ChatGPT-4o integration. Camera, WiFi, app, account all required. Camera=yes, Internet Access=yes per Product Matrix. Voice=4: excellent AI voice response but conversational not animal-mimicry. Not recommended for seniors or dementia care. Review Strength=4: 1,199 reviews, 4.2★ (repo data, 2026-06-22). DEMENTIA SUITABILITY EVIDENCE TIER (2026-07-02): Tier D — no dementia-specific evidence found (independent or manufacturer); score reflects general sub-criteria judgment only (simplicity, familiar form, calmness, safety). Capped at 3. Score is provisional pending dementia consultant review. DEMENTIA SUITABILITY RECALCULATED (2026-07-02, Tim-directed methodology): Simplicity=1, Familiar Form=2, Safety=2, Calmness=avg(Sound=3, Behavioral Realism=2)=2.5. Raw average of 4 sub-criteria=1.88, rounded=2, Evidence Tier D cap=3 -&gt; Final=2 (was 1). This is a first-pass 'best effort' score pending dementia care consultant review (consultant search in progress as of 2026-07-02). Products in the 'Ai &amp; Robotic Pets' Type category are excluded from memory-care-relevant Best For lists via a separate Type filter in the Best For Weighting Table, independent of this score.</t>
+          <t>Children's programmable toy robot dog with remote/gesture control. No WiFi or app required (infrared remote — Privacy=5). Hard plastic ABS shell, LED facial expressions, walks/spins/dances. 30-day returns, 90-day warranty per Amazon listing (B0FLXCXPHD). Sound Level Control=2: no volume adjustment noted; on/off states only. Dementia=1: remote-controlled, LED face, not a calming companion product. Not recommended for senior care use cases. Review Strength=3: 283 reviews, 4.4★ (repo data, 2026-06-22). DEMENTIA SUITABILITY EVIDENCE TIER (2026-07-02): Tier D — no dementia-specific evidence found (independent or manufacturer); score reflects general sub-criteria judgment only (simplicity, familiar form, calmness, safety). Capped at 3. Score is provisional pending dementia consultant review. DEMENTIA SUITABILITY RECALCULATED (2026-07-02, Tim-directed methodology): Simplicity=3, Familiar Form=3, Safety=3, Calmness=avg(Sound=2, Behavioral Realism=2)=2.0. Raw average of 4 sub-criteria=2.75, rounded=3, Evidence Tier D cap=3 -&gt; Final=3 (was 1). This is a first-pass 'best effort' score pending dementia care consultant review (consultant search in progress as of 2026-07-02). Products in the 'Ai &amp; Robotic Pets' Type category are excluded from memory-care-relevant Best For lists via a separate Type filter in the Best For Weighting Table, independent of this score.</t>
         </is>
       </c>
     </row>
@@ -1630,12 +1628,12 @@
       </c>
       <c r="B18" s="11" t="inlineStr">
         <is>
-          <t>Enabot</t>
+          <t>Loona</t>
         </is>
       </c>
       <c r="C18" s="11" t="inlineStr">
         <is>
-          <t>EBO Air 2 Plus FamilyBot</t>
+          <t>Robot Pet Dog</t>
         </is>
       </c>
       <c r="D18" s="12" t="inlineStr">
@@ -1645,48 +1643,48 @@
       </c>
       <c r="E18" s="12" t="inlineStr">
         <is>
-          <t>Robot</t>
+          <t>Dog</t>
         </is>
       </c>
       <c r="F18" s="12" t="n">
-        <v>359</v>
+        <v>499</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>5</v>
+        <v>4.2</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>42</v>
-      </c>
-      <c r="I18" s="17" t="n">
-        <v>1.75</v>
+        <v>1199</v>
+      </c>
+      <c r="I18" s="16" t="n">
+        <v>2.35</v>
       </c>
       <c r="J18" s="12" t="n">
         <v>5</v>
       </c>
       <c r="K18" s="12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L18" s="12" t="n">
         <v>2</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N18" s="12" t="n">
         <v>2</v>
       </c>
       <c r="O18" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="P18" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="P18" s="12" t="n">
-        <v>1</v>
-      </c>
       <c r="Q18" s="12" t="n">
         <v>3</v>
       </c>
       <c r="R18" s="11" t="inlineStr">
         <is>
-          <t>Camera=yes, Internet Access=yes per Product Matrix. Hard-shell rolling security camera robot; not a companion pet. Scores are category-level; minor spec differences between models noted. Review strength and Value estimated — recommend manual Amazon verification. Air 2 Plus has AI chat mode — highest AI tier in Enabot lineup per manufacturer. Product renamed to 'EBO Air 2 Plus FamilyBot'. Review Strength=3: 42 reviews, 5★ (repo data, 2026-06-22). DEMENTIA SUITABILITY EVIDENCE TIER (2026-07-02): Tier D — no dementia-specific evidence found (independent or manufacturer); score reflects general sub-criteria judgment only (simplicity, familiar form, calmness, safety). Capped at 3. Score is provisional pending dementia consultant review. DEMENTIA SUITABILITY RECALCULATED (2026-07-02, Tim-directed methodology): Simplicity=2, Familiar Form=1, Safety=2, Calmness=avg(Sound=3, Behavioral Realism=1)=2.0. Raw average of 4 sub-criteria=1.75, rounded=2, Evidence Tier D cap=3 -&gt; Final=2 (was 1). This is a first-pass 'best effort' score pending dementia care consultant review (consultant search in progress as of 2026-07-02). Products in the 'Ai &amp; Robotic Pets' Type category are excluded from memory-care-relevant Best For lists via a separate Type filter in the Best For Weighting Table, independent of this score.</t>
+          <t>KEYi Tech Loona. Rubric anchor product: Control Accessibility=1 (worst) and Customization Options=5 (best). ChatGPT-4o integration. Camera, WiFi, app, account all required. Camera=yes, Internet Access=yes per Product Matrix. Voice=4: excellent AI voice response but conversational not animal-mimicry. Not recommended for seniors or dementia care. Review Strength=4: 1,199 reviews, 4.2★ (repo data, 2026-06-22). DEMENTIA SUITABILITY EVIDENCE TIER (2026-07-02): Tier D — no dementia-specific evidence found (independent or manufacturer); score reflects general sub-criteria judgment only (simplicity, familiar form, calmness, safety). Capped at 3. Score is provisional pending dementia consultant review. DEMENTIA SUITABILITY RECALCULATED (2026-07-02, Tim-directed methodology): Simplicity=1, Familiar Form=2, Safety=2, Calmness=avg(Sound=3, Behavioral Realism=2)=2.5. Raw average of 4 sub-criteria=1.88, rounded=2, Evidence Tier D cap=3 -&gt; Final=2 (was 1). This is a first-pass 'best effort' score pending dementia care consultant review (consultant search in progress as of 2026-07-02). Products in the 'Ai &amp; Robotic Pets' Type category are excluded from memory-care-relevant Best For lists via a separate Type filter in the Best For Weighting Table, independent of this score.</t>
         </is>
       </c>
     </row>
@@ -1701,12 +1699,12 @@
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
-          <t>EBO Air 2 FamilyBot</t>
+          <t>EBO Air 2 Plus FamilyBot</t>
         </is>
       </c>
       <c r="D19" s="8" t="inlineStr">
         <is>
-          <t>Best Value</t>
+          <t>Premium</t>
         </is>
       </c>
       <c r="E19" s="8" t="inlineStr">
@@ -1715,15 +1713,15 @@
         </is>
       </c>
       <c r="F19" s="8" t="n">
-        <v>179</v>
+        <v>359</v>
       </c>
       <c r="G19" s="8" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="H19" s="8" t="n">
-        <v>72</v>
-      </c>
-      <c r="I19" s="16" t="n">
+        <v>42</v>
+      </c>
+      <c r="I19" s="17" t="n">
         <v>1.75</v>
       </c>
       <c r="J19" s="8" t="n">
@@ -1751,6 +1749,72 @@
         <v>3</v>
       </c>
       <c r="R19" s="7" t="inlineStr">
+        <is>
+          <t>Camera=yes, Internet Access=yes per Product Matrix. Hard-shell rolling security camera robot; not a companion pet. Scores are category-level; minor spec differences between models noted. Review strength and Value estimated — recommend manual Amazon verification. Air 2 Plus has AI chat mode — highest AI tier in Enabot lineup per manufacturer. Product renamed to 'EBO Air 2 Plus FamilyBot'. Review Strength=3: 42 reviews, 5★ (repo data, 2026-06-22). DEMENTIA SUITABILITY EVIDENCE TIER (2026-07-02): Tier D — no dementia-specific evidence found (independent or manufacturer); score reflects general sub-criteria judgment only (simplicity, familiar form, calmness, safety). Capped at 3. Score is provisional pending dementia consultant review. DEMENTIA SUITABILITY RECALCULATED (2026-07-02, Tim-directed methodology): Simplicity=2, Familiar Form=1, Safety=2, Calmness=avg(Sound=3, Behavioral Realism=1)=2.0. Raw average of 4 sub-criteria=1.75, rounded=2, Evidence Tier D cap=3 -&gt; Final=2 (was 1). This is a first-pass 'best effort' score pending dementia care consultant review (consultant search in progress as of 2026-07-02). Products in the 'Ai &amp; Robotic Pets' Type category are excluded from memory-care-relevant Best For lists via a separate Type filter in the Best For Weighting Table, independent of this score.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="45" customHeight="1">
+      <c r="A20" s="10" t="n">
+        <v>16</v>
+      </c>
+      <c r="B20" s="11" t="inlineStr">
+        <is>
+          <t>Enabot</t>
+        </is>
+      </c>
+      <c r="C20" s="11" t="inlineStr">
+        <is>
+          <t>EBO Air 2 FamilyBot</t>
+        </is>
+      </c>
+      <c r="D20" s="12" t="inlineStr">
+        <is>
+          <t>Best Value</t>
+        </is>
+      </c>
+      <c r="E20" s="12" t="inlineStr">
+        <is>
+          <t>Robot</t>
+        </is>
+      </c>
+      <c r="F20" s="12" t="n">
+        <v>179</v>
+      </c>
+      <c r="G20" s="12" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H20" s="12" t="n">
+        <v>72</v>
+      </c>
+      <c r="I20" s="16" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="J20" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="K20" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="L20" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="M20" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="N20" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="O20" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="P20" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q20" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="R20" s="11" t="inlineStr">
         <is>
           <t>Camera=yes, Internet Access=yes per Product Matrix. Hard-shell rolling security camera robot; not a companion pet. Scores are category-level; minor spec differences between models noted. Review strength and Value estimated — recommend manual Amazon verification. Product renamed in repo to 'EBO Air 2 FamilyBot'. Review Strength=3: 72 reviews, 4.5★ (repo data, 2026-06-22). DEMENTIA SUITABILITY EVIDENCE TIER (2026-07-02): Tier D — no dementia-specific evidence found (independent or manufacturer); score reflects general sub-criteria judgment only (simplicity, familiar form, calmness, safety). Capped at 3. Score is provisional pending dementia consultant review. DEMENTIA SUITABILITY RECALCULATED (2026-07-02, Tim-directed methodology): Simplicity=2, Familiar Form=1, Safety=2, Calmness=avg(Sound=3, Behavioral Realism=1)=2.0. Raw average of 4 sub-criteria=1.75, rounded=2, Evidence Tier D cap=3 -&gt; Final=2 (was 1). This is a first-pass 'best effort' score pending dementia care consultant review (consultant search in progress as of 2026-07-02). Products in the 'Ai &amp; Robotic Pets' Type category are excluded from memory-care-relevant Best For lists via a separate Type filter in the Best For Weighting Table, independent of this score.</t>
         </is>
@@ -1772,7 +1836,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H16"/>
+  <dimension ref="A1:H15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -2032,7 +2096,7 @@
       </c>
       <c r="B8" s="20" t="inlineStr">
         <is>
-          <t>Grey Tabby Cat</t>
+          <t>Original Siamese Cat</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr">
@@ -2049,16 +2113,16 @@
         <v>3.75</v>
       </c>
       <c r="F8" s="20" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="G8" s="20" t="inlineStr">
         <is>
-          <t>Original Black and White Shorthair Cat</t>
+          <t>Grey Tabby Cat</t>
         </is>
       </c>
       <c r="H8" s="20" t="inlineStr">
         <is>
-          <t>score=3.75 rating=4.3</t>
+          <t>score=3.75 rating=4.1</t>
         </is>
       </c>
     </row>
@@ -2070,7 +2134,7 @@
       </c>
       <c r="B9" s="19" t="inlineStr">
         <is>
-          <t>Original Siamese Cat</t>
+          <t>Original Plush White Cat</t>
         </is>
       </c>
       <c r="C9" s="19" t="inlineStr">
@@ -2087,16 +2151,16 @@
         <v>3.75</v>
       </c>
       <c r="F9" s="19" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="G9" s="19" t="inlineStr">
         <is>
-          <t>Original Black and White Shorthair Cat</t>
+          <t>Grey Tabby Cat</t>
         </is>
       </c>
       <c r="H9" s="19" t="inlineStr">
         <is>
-          <t>score=3.75 rating=4.1</t>
+          <t>score=3.75 rating=4</t>
         </is>
       </c>
     </row>
@@ -2108,24 +2172,24 @@
       </c>
       <c r="B10" s="20" t="inlineStr">
         <is>
-          <t>Original Plush White Cat</t>
+          <t>Original Beagle</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr">
         <is>
-          <t>Budget Friendly</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D10" s="20" t="inlineStr">
         <is>
-          <t>Cat</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E10" s="20" t="n">
         <v>3.75</v>
       </c>
       <c r="F10" s="20" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G10" s="20" t="inlineStr">
         <is>
@@ -2134,7 +2198,7 @@
       </c>
       <c r="H10" s="20" t="inlineStr">
         <is>
-          <t>score=3.75 rating=4</t>
+          <t>score=3.75 rating=0</t>
         </is>
       </c>
     </row>
@@ -2146,33 +2210,33 @@
       </c>
       <c r="B11" s="19" t="inlineStr">
         <is>
-          <t>Original Chocolate Lab</t>
+          <t>Original Shih Tzu</t>
         </is>
       </c>
       <c r="C11" s="19" t="inlineStr">
         <is>
-          <t>Budget Friendly</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D11" s="19" t="inlineStr">
         <is>
-          <t>Dog</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E11" s="19" t="n">
         <v>3.75</v>
       </c>
       <c r="F11" s="19" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="G11" s="19" t="inlineStr">
         <is>
-          <t>Original Beagle</t>
+          <t>Original Black and White Shorthair Cat</t>
         </is>
       </c>
       <c r="H11" s="19" t="inlineStr">
         <is>
-          <t>score=3.75 rating=4.3</t>
+          <t>score=3.75 rating=0</t>
         </is>
       </c>
     </row>
@@ -2205,7 +2269,7 @@
       </c>
       <c r="G12" s="20" t="inlineStr">
         <is>
-          <t>Original Beagle</t>
+          <t>Original Chocolate Lab</t>
         </is>
       </c>
       <c r="H12" s="20" t="inlineStr">
@@ -2217,38 +2281,38 @@
     <row r="13" ht="18" customHeight="1">
       <c r="A13" s="19" t="inlineStr">
         <is>
-          <t>Perfect Petzzz</t>
+          <t>Enabot</t>
         </is>
       </c>
       <c r="B13" s="19" t="inlineStr">
         <is>
-          <t>Original Shih Tzu</t>
+          <t>EBO Air 2S FamilyBot</t>
         </is>
       </c>
       <c r="C13" s="19" t="inlineStr">
         <is>
-          <t>Budget Friendly</t>
+          <t>Premium</t>
         </is>
       </c>
       <c r="D13" s="19" t="inlineStr">
         <is>
-          <t>Dog</t>
+          <t>Robot</t>
         </is>
       </c>
       <c r="E13" s="19" t="n">
-        <v>3.75</v>
+        <v>1.75</v>
       </c>
       <c r="F13" s="19" t="n">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="G13" s="19" t="inlineStr">
         <is>
-          <t>Original Beagle</t>
+          <t>EBO Air 2 Plus FamilyBot</t>
         </is>
       </c>
       <c r="H13" s="19" t="inlineStr">
         <is>
-          <t>score=3.75 rating=4.2</t>
+          <t>score=1.75 rating=5</t>
         </is>
       </c>
     </row>
@@ -2260,7 +2324,7 @@
       </c>
       <c r="B14" s="20" t="inlineStr">
         <is>
-          <t>EBO Air 2S FamilyBot</t>
+          <t>EBO X FamilyBot</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr">
@@ -2277,7 +2341,7 @@
         <v>1.75</v>
       </c>
       <c r="F14" s="20" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="G14" s="20" t="inlineStr">
         <is>
@@ -2286,7 +2350,7 @@
       </c>
       <c r="H14" s="20" t="inlineStr">
         <is>
-          <t>score=1.75 rating=5</t>
+          <t>score=1.75 rating=4.5</t>
         </is>
       </c>
     </row>
@@ -2298,12 +2362,12 @@
       </c>
       <c r="B15" s="19" t="inlineStr">
         <is>
-          <t>EBO X FamilyBot</t>
+          <t>ROLA Mini Pet Monitor</t>
         </is>
       </c>
       <c r="C15" s="19" t="inlineStr">
         <is>
-          <t>Premium</t>
+          <t>Best Value</t>
         </is>
       </c>
       <c r="D15" s="19" t="inlineStr">
@@ -2312,55 +2376,17 @@
         </is>
       </c>
       <c r="E15" s="19" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="F15" s="19" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="G15" s="19" t="inlineStr">
         <is>
-          <t>EBO Air 2 Plus FamilyBot</t>
+          <t>EBO Air 2 FamilyBot</t>
         </is>
       </c>
       <c r="H15" s="19" t="inlineStr">
-        <is>
-          <t>score=1.75 rating=4.5</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="18" customHeight="1">
-      <c r="A16" s="20" t="inlineStr">
-        <is>
-          <t>Enabot</t>
-        </is>
-      </c>
-      <c r="B16" s="20" t="inlineStr">
-        <is>
-          <t>ROLA Mini Pet Monitor</t>
-        </is>
-      </c>
-      <c r="C16" s="20" t="inlineStr">
-        <is>
-          <t>Best Value</t>
-        </is>
-      </c>
-      <c r="D16" s="20" t="inlineStr">
-        <is>
-          <t>Robot</t>
-        </is>
-      </c>
-      <c r="E16" s="20" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="F16" s="20" t="n">
-        <v>5</v>
-      </c>
-      <c r="G16" s="20" t="inlineStr">
-        <is>
-          <t>EBO Air 2 FamilyBot</t>
-        </is>
-      </c>
-      <c r="H16" s="20" t="inlineStr">
         <is>
           <t>score=1.70 rating=5</t>
         </is>

--- a/Documentation/Best For Lists/Best for Seniors Living Alone List.xlsx
+++ b/Documentation/Best For Lists/Best for Seniors Living Alone List.xlsx
@@ -621,7 +621,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-07-07  |  Products shown: 16  |  Eliminated by dedup rule: 13</t>
+          <t>Generated: 2026-07-08  |  Products shown: 16  |  Eliminated by dedup rule: 13</t>
         </is>
       </c>
     </row>

--- a/Documentation/Best For Lists/Best for Seniors Living Alone List.xlsx
+++ b/Documentation/Best For Lists/Best for Seniors Living Alone List.xlsx
@@ -621,7 +621,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-07-08  |  Products shown: 16  |  Eliminated by dedup rule: 13</t>
+          <t>Generated: 2026-07-11  |  Products shown: 16  |  Eliminated by dedup rule: 13</t>
         </is>
       </c>
     </row>
@@ -1379,7 +1379,7 @@
       </c>
       <c r="E14" s="12" t="inlineStr">
         <is>
-          <t>Robot</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="F14" s="12" t="n">
